--- a/artfynd/A 54783-2025 artfynd.xlsx
+++ b/artfynd/A 54783-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206162</v>
       </c>
       <c r="B2" t="n">
-        <v>57655</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136206158</v>
       </c>
       <c r="B3" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136206163</v>
       </c>
       <c r="B4" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136206170</v>
       </c>
       <c r="B5" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>136206172</v>
       </c>
       <c r="B6" t="n">
-        <v>58868</v>
+        <v>58870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
